--- a/www/download/COUNTRY.ROW.WIOD16.xlsx
+++ b/www/download/COUNTRY.ROW.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>Resto do mundo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.767</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.054</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>1.284</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.599</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.886</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.772</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2.131</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2.469</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2.604</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2.596</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2.581</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>947.617</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>974.461</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>1000.729</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1033.017</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1066.89</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1091.838</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1119.505</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>1147.144</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>1172.476</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>1193.77</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>1218.07</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>1281.007</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>1356.393</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>1428.937</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1491.948</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>409.877</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>422.385</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>434.77</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>449.701</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>467.937</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>481.536</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>498.298</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>515.048</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>530.111</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>541.019</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>554.202</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>584.006</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>623.348</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>661.666</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>695.348</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1749326.228</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1823779.121</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1894668.559</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1972878.065</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2061628.419</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2095774.127</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2153261.884</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2217351.867</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2290607.861</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2333155.69</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2392411.796</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>2540846.285</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>2704019.78</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2869503.873</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>3005334.063</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>756644.638</t>
+          <t>2575730603353.02</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>790526.622</t>
+          <t>2624714683855.6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>823145.14</t>
+          <t>2794855978692.23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>858848.102</t>
+          <t>2908506966635.87</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>904228.799</t>
+          <t>3000337536772.91</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>924304.549</t>
+          <t>3149535728895.15</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>958428.493</t>
+          <t>3292708248510.7</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>995552.657</t>
+          <t>3305428730331.72</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1035652.129</t>
+          <t>3401180004097.76</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1057391.769</t>
+          <t>3501593341422.3</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1088507.47</t>
+          <t>3496560198653.37</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1158361.996</t>
+          <t>3667617027422.46</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1242666.113</t>
+          <t>3936264189263.31</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1328716.665</t>
+          <t>4121825177276.58</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1400688.27</t>
+          <t>4283454105582.91</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>784137847169.266</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>793756301921.496</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>843267758953.288</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>852304675381.817</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>835259375511.156</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>864995539184.223</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>892235073256.426</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>860552604730.381</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>871108774400.428</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>884939209251.114</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>863424222697.806</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>863017607364.134</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>915715741886.067</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>948180867772.27</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>977074465481.708</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>16802031.0305368</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>17252196.9716406</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>17726185.2683816</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>17016659.5487355</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>15560011.8218863</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>13979255.2454916</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>12458708.1815472</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>10448633.5705591</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>9194510.77014501</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>9727075.27482761</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>8470723.22198249</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>7783863.78196208</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>7817716.18539073</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>7710382.54007952</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>7759152.4321359</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>12150718.566696</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>12378920.8293366</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>13106463.6180246</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>14685555.5993683</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>16678581.8681418</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>18188385.5277525</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>19799269.2348297</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>22740038.2652249</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>25268393.6572079</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>23288915.9234548</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>26024818.3016252</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>28839939.9413264</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>29717421.4605604</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>31171945.9154165</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>32595173.0464048</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>20928754.2959547</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>21126311.9652425</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>22630797.9416875</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>25630547.7495081</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>29231282.3971624</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>32945658.7860837</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>36387112.7618615</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>41242148.8545518</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>46060957.8720781</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>43154599.170116</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>47741479.4565505</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>53180164.7411287</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>55611543.7946977</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>58175268.9562369</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>60736549.2796353</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.0350617039293791</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.00406885638859855</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.0238626690142154</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.00767733235843049</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.0825724627063193</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.0685656826045553</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.0741883187161527</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.156876002455217</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.188889561685891</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.194875035845896</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.260686741751302</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.342222900110043</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.357043519139798</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.401332498689111</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.43355324443708</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>781944.362003292</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>776989.344365054</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>765971.325364832</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>876822.096730077</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1052946.58653483</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>1283466.47039423</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>1430685.15599202</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>1597573.79948083</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>1885221.05623634</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1770782.01170685</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>2129205.60093568</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2467475.73005486</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2602486.12832423</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2596470.76078158</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2581890.77681025</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1913.10383175129</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1879.22346861709</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1939.572486252</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1895.27129012408</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1784.98145518585</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1796.32485944626</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1790.56544520123</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1670.8200990491</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1643.25655236167</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1635.68825933851</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1557.96077177193</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1477.75397609249</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1469.02910669001</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1433.02110933307</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1405.15866702003</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.578</t>
+          <t>-313584529212.894</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>-319427621326.702</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.515</t>
+          <t>-339312611279.89</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.682</t>
+          <t>-373391102895.296</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.964</t>
+          <t>-396843816578.949</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.304</t>
+          <t>-389770766142.525</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>-390135379790.485</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>3.173</t>
+          <t>-395197408433.072</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3.804</t>
+          <t>-393472330130.153</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3.601</t>
+          <t>-375665388817.272</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>4.151</t>
+          <t>-380327631752.675</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>4.79</t>
+          <t>-429542908252.145</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>5.184</t>
+          <t>-417264077858.03</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>5.353</t>
+          <t>-430956474561.763</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>5.459</t>
+          <t>-448804553281.254</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.801</t>
+          <t>-282178207284.785</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.789</t>
+          <t>-287034198242.326</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.729</t>
+          <t>-302211158680.04</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.921</t>
+          <t>-330766063655.196</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.243</t>
+          <t>-347463733247.541</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.632</t>
+          <t>-337603776908.816</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3.068</t>
+          <t>-332493570293.817</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>3.612</t>
+          <t>-333756322868.663</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>4.328</t>
+          <t>-331371125535.913</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>-313877927418.026</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>4.726</t>
+          <t>-315921777706.739</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>5.445</t>
+          <t>-355572677280.647</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>5.882</t>
+          <t>-339387327879.217</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>6.059</t>
+          <t>-351301860030.222</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>6.161</t>
+          <t>-367579811670.854</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8.865</t>
+          <t>-31406321928.1093</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8.933</t>
+          <t>-32393423084.3763</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>8.876</t>
+          <t>-37101452599.8499</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>10.105</t>
+          <t>-42625039240.1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>11.913</t>
+          <t>-49380083331.4086</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>14.159</t>
+          <t>-52166989233.7093</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>16.271</t>
+          <t>-57641809496.6682</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>18.998</t>
+          <t>-61441085564.4095</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>22.614</t>
+          <t>-62101204594.2398</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>22.319</t>
+          <t>-61787461399.2461</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>25.893</t>
+          <t>-64405854045.9368</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>30.277</t>
+          <t>-73970230971.4977</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>33.112</t>
+          <t>-77876749978.8126</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>33.912</t>
+          <t>-79654614531.5413</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>34.523</t>
+          <t>-81224741610.3999</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6.282</t>
+          <t>1846.02715161627</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6.238</t>
+          <t>1871.5771782012</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6.102</t>
+          <t>1893.28910998349</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6.966</t>
+          <t>1909.82191772775</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>8.386</t>
+          <t>1932.37176982565</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>10.238</t>
+          <t>1919.49109961373</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>12.034</t>
+          <t>1923.40448513195</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>14.426</t>
+          <t>1932.93167700976</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>17.207</t>
+          <t>1953.65056227474</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>16.121</t>
+          <t>1954.44306750981</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>18.942</t>
+          <t>1964.10048914149</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>21.914</t>
+          <t>1983.47522744001</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>1993.53642866141</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>24.993</t>
+          <t>2008.13905181596</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>2014.36976605544</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2.988</t>
+          <t>1846.02715161627</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2.976</t>
+          <t>1871.5771782012</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2.902</t>
+          <t>1893.28910998349</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>3.243</t>
+          <t>1909.82191772775</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>3.834</t>
+          <t>1932.37176982565</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>4.547</t>
+          <t>1919.49109961373</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>5.321</t>
+          <t>1923.40448513195</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>1932.93167700976</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>7.537</t>
+          <t>1953.65056227474</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>7.035</t>
+          <t>1954.44306750981</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>8.242</t>
+          <t>1964.10048914149</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>9.494</t>
+          <t>1983.47522744001</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>1993.53642866141</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>10.529</t>
+          <t>2008.13905181596</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>10.689</t>
+          <t>2014.36976605544</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>1250328.5957678</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1176527.35817282</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1180573.52898547</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>1353836.03136853</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>1648055.16684282</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>1965675.1830866</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2337867.00145249</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2675641.16316839</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>3154334.97338898</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>2427567.61712097</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>3046604.1485698</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>3754369.14238384</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>3883072.69217882</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>3890077.3038656</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>3833149.18435125</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>412251333724.621</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>412373980518.96</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>428824445698.802</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>473723958841.865</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>512058508708.61</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>520773097794.958</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>534784751282.826</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>525025948997.444</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>529396362371.042</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>470737538055.514</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>500818688763.821</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>582493393000.638</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>579523091877.214</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>588226300871.978</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>591264981014.32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>1378209.57677912</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1321696.78592474</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1405929.29902574</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1602240.94897694</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1959537.08254679</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2255962.82659254</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2693843.61612477</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>3320527.4593043</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>3875264.41781774</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>3244053.69155687</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>3831977.58746153</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>4458230.38009404</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>4730745.92333863</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>4924830.72112422</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>5099349.33097797</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1749326.228</t>
+          <t>118424537359.06</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1823779.121</t>
+          <t>116186516780.318</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1894668.559</t>
+          <t>125901284659.152</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1972878.065</t>
+          <t>138126815664.327</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2061628.419</t>
+          <t>158197634819.49</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2095774.127</t>
+          <t>167605301184.173</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2153261.884</t>
+          <t>185503723210.72</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2217351.867</t>
+          <t>192898872467.541</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2290607.861</t>
+          <t>197989918016.186</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2333155.69</t>
+          <t>174556938322.022</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2392411.796</t>
+          <t>188412334664.597</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>2540846.285</t>
+          <t>210701823157.981</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>2704019.78</t>
+          <t>232555750747.973</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2869503.873</t>
+          <t>243558020831.663</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>3005334.063</t>
+          <t>247018255761.573</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>756644.638</t>
+          <t>-127880.981011328</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>790526.622</t>
+          <t>-145169.42775192</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>823145.14</t>
+          <t>-225355.770040267</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>858848.102</t>
+          <t>-248404.917608404</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>904228.799</t>
+          <t>-311481.915703973</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>924304.549</t>
+          <t>-290287.643505938</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>958428.493</t>
+          <t>-355976.614672273</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>995552.657</t>
+          <t>-644886.296135904</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1035652.129</t>
+          <t>-720929.444428757</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1057391.769</t>
+          <t>-816486.074435896</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1088507.47</t>
+          <t>-785373.438891732</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1158361.996</t>
+          <t>-703861.237710196</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1242666.113</t>
+          <t>-847673.231159813</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>1328716.665</t>
+          <t>-1034753.41725862</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>1400688.27</t>
+          <t>-1266200.14662673</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2575755.568</t>
+          <t>293826796365.561</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2624857.49</t>
+          <t>296187463738.642</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2794971.317</t>
+          <t>302923161039.65</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2908591.885</t>
+          <t>335597143177.538</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3000494.641</t>
+          <t>353860873889.12</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3149706.911</t>
+          <t>353167796610.785</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3292823.966</t>
+          <t>349281028072.105</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3305531.961</t>
+          <t>332127076529.903</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3401263.291</t>
+          <t>331406444354.856</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>3501719.759</t>
+          <t>296180599733.492</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>3496785.781</t>
+          <t>312406354099.224</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>3667927.15</t>
+          <t>371791569842.657</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>3936326.315</t>
+          <t>346967341129.241</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>4121844.364</t>
+          <t>344668280040.315</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>4283346.951</t>
+          <t>344246725252.747</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>20.928</t>
+          <t>1712202.9010106</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>21.124</t>
+          <t>1680774.9880007</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>22.628</t>
+          <t>1686428.8850896</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>25.629</t>
+          <t>1888201.339026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>29.23</t>
+          <t>2246502.99383557</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>32.945</t>
+          <t>2709922.29373356</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>36.388</t>
+          <t>3175033.58916532</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>41.238</t>
+          <t>3724645.85134205</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>46.058</t>
+          <t>4523439.75709824</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>43.155</t>
+          <t>3994833.3445394</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>4789168.7436207</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>53.175</t>
+          <t>5620537.1099294</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>55.608</t>
+          <t>5990354.69562486</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>58.175</t>
+          <t>6102676.84317341</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>60.735</t>
+          <t>6165912.1706269</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1495405.662</t>
+          <t>-0.0882014830826021</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1537946.392</t>
+          <t>-0.0869834523484495</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1618620.709</t>
+          <t>-0.0862978898732557</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1666489.581</t>
+          <t>-0.0867750174559267</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1711911.731</t>
+          <t>-0.0883831479626817</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1738771.425</t>
+          <t>-0.0906443856873615</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1791656.776</t>
+          <t>-0.087926507895471</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1822542.663</t>
+          <t>-0.0840899432459838</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1865839.514</t>
+          <t>-0.0833656447693189</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1889678.377</t>
+          <t>-0.0793403613620728</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1906043.652</t>
+          <t>-0.0822309853517786</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1988971.928</t>
+          <t>-0.0814973692453236</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2103441.37</t>
+          <t>-0.078595516557578</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2208589.901</t>
+          <t>-0.076565522128032</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2298779.392</t>
+          <t>-0.0747874866790589</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>1577655.48872709</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>12.377</t>
+          <t>1570397.31840218</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>13.104</t>
+          <t>1515050.17604674</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>14.684</t>
+          <t>1682181.16082903</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>16.677</t>
+          <t>1963842.74565605</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>18.187</t>
+          <t>2303560.02040457</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>19.799</t>
+          <t>2690001.09120825</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>22.737</t>
+          <t>3173291.60349065</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>25.266</t>
+          <t>3804383.88642882</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>23.288</t>
+          <t>3600867.44926011</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>26.022</t>
+          <t>4150857.06519537</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>28.835</t>
+          <t>4790426.73723502</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>29.715</t>
+          <t>5183989.64825557</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>31.171</t>
+          <t>5353375.60454835</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>32.595</t>
+          <t>5459132.07974466</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>784145.643</t>
+          <t>1800814.50077968</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>793783.161</t>
+          <t>1789202.57038073</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>843291.321</t>
+          <t>1728612.29782657</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>852325.494</t>
+          <t>1921291.95444887</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>835279.28</t>
+          <t>2242788.54385591</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>865014.563</t>
+          <t>2632073.64092198</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>892263.011</t>
+          <t>3067601.81602745</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>860580.123</t>
+          <t>3611752.4499459</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>871091.336</t>
+          <t>4328141.77644798</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>884945.85</t>
+          <t>4090391.87821205</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>863456.849</t>
+          <t>4725835.92444684</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>863065.165</t>
+          <t>5445439.58486657</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>915735.237</t>
+          <t>5882302.32646808</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>948179.837</t>
+          <t>6059367.5567379</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>977060.384</t>
+          <t>6160678.94237295</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>8865433.2634179</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>8932611.01263824</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-2.39</t>
+          <t>8875898.6632211</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>10104545.3223379</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>8.25</t>
+          <t>11913431.585164</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>14159359.795553</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>16271374.6995712</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>18998393.1230342</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>22613884.4298864</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>22318804.4685833</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>25892984.1570922</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>34.21</t>
+          <t>30276753.1382179</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>33112399.3111959</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>33911748.8997174</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>43.36</t>
+          <t>34523031.7458068</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>16.802</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>17.253</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>17.727</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>17.017</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>15.561</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>13.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>12.459</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>10.449</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>9.195</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>9.727</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>8.471</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>7.785</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>7.818</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>7.759</t>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>756644638131.996</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>790526621521.432</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>823145139531.026</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>858848101645.368</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>904228799145.655</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>924304548778.285</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>958428493240.903</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>995552657262.908</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1035652128977.66</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1057391769375.36</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1088507470062.05</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1158361995802.32</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1242666112900.78</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>1328716664644.52</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1400688270047.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>1749326227674.04</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1823779120993.5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>1894668558535.74</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1972878064906.69</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2061628418959.29</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2095774127486.82</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2153261884442.65</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2217351866773.18</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2290607861353.38</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2333155690282.16</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2392411796388.16</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>2540846285389.31</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2704019780088.7</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2869503872990.63</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>3005334063447.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1495405661626.89</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1537946392370.84</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1618620708679.12</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1666489580602.14</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1711911730700.66</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1738771424864.42</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1791656775591.68</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1822542663230.35</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1865839513829.65</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1889678377153.93</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1906043651903.69</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1988971928040.04</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>2103441370451.62</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2208589900899.68</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2298779391713.35</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>947616738</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>974461081.4</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1000728599</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1033016768</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1066890156</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>1091838419</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1119505492</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>1147144461</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>1172475726</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1193770097</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1218069956</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1281007320</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1356393463</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1428936841</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1491947563</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>409877307.313451</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>422385264.539941</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>434769911.890637</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>449700620.60404</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>467937284.773746</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>481536251.438879</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>498297940.266659</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>515048032.532131</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>530111243.523405</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>541019478.619352</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>554201516.714572</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>584006283.404593</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>623347582.233643</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>661665666.749006</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>695348139.974701</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>1749326227674.04</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1823779120993.5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>1894668558535.74</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1972878064906.69</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>2061628418959.29</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2095774127486.82</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2153261884442.65</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2217351866773.18</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2290607861353.38</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2333155690282.16</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2392411796388.16</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>2540846285389.31</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>2704019780088.7</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2869503872990.63</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>3005334063447.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>756644638131.996</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>790526621521.432</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>823145139531.026</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>858848101645.368</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>904228799145.655</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>924304548778.285</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>958428493240.903</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>995552657262.908</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>1035652128977.66</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1057391769375.36</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1088507470062.05</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1158361995802.32</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>1242666112900.78</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>1328716664644.52</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>1400688270047.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>6282373.40824366</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6238270.61609571</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>6101632.58173948</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>6965917.30344096</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>8386045.57491782</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>10238049.620376</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>12034154.3281908</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>14425536.2949305</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>17207030.3041438</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>16121440.6048166</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>18942147.6317154</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>21913614.9280403</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>23810255.6391664</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>24992542.1349743</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>25610236.5866257</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2988186.09702126</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2975564.63983902</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2901766.62555792</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>3242773.07776634</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>3833605.96402527</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>4546855.35921803</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5321482.32542044</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6319813.09397517</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>7537349.90733164</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>7034512.27976041</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>8241860.11794752</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>9494132.67138763</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>10189621.2126757</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>10528582.5882739</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>10688523.5929504</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
